--- a/llm_result_ServiceCode4.xlsx
+++ b/llm_result_ServiceCode4.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="37">
   <si>
     <t>行番号</t>
   </si>
@@ -37,12 +37,6 @@
     <t>修正アドバイス</t>
   </si>
   <si>
-    <t>7</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
     <t>1234</t>
   </si>
   <si>
@@ -52,6 +46,27 @@
     <t>2000000001</t>
   </si>
   <si>
+    <t>2000000002</t>
+  </si>
+  <si>
+    <t>2000000003</t>
+  </si>
+  <si>
+    <t>2000000004</t>
+  </si>
+  <si>
+    <t>2000000005</t>
+  </si>
+  <si>
+    <t>2000000006</t>
+  </si>
+  <si>
+    <t>2000000007</t>
+  </si>
+  <si>
+    <t>2000000008</t>
+  </si>
+  <si>
     <t>WBSマスタ登録可否フラグ</t>
   </si>
   <si>
@@ -64,16 +79,52 @@
     <t>9999999999</t>
   </si>
   <si>
-    <t>親値がYの場合、WBSマスタ登録可否フラグはNULLである必要があります。</t>
-  </si>
-  <si>
-    <t>親値がNの場合、サービスコードと費用仕訳レベルは一致する必要があります。</t>
+    <t>1111111111</t>
+  </si>
+  <si>
+    <t>0000000000</t>
+  </si>
+  <si>
+    <t>チェック2：親値が'Y'の場合、WBSマスタ登録可否フラグはNULLでなければならない。</t>
+  </si>
+  <si>
+    <t>チェック3：親値が'N'の場合、サービスコードと費用仕訳レベルは一致しなければならない。</t>
+  </si>
+  <si>
+    <t>チェック4－01：サービスコードが'0000000000'以外（2000000002）の場合でも、チェック3により子値(N)はサービスコード＝費用仕訳レベルである必要がある。また、本行は名称から4-01の検証用と推測されるが、サービスコードが0埋めではないため条件外かつチェック3違反。</t>
+  </si>
+  <si>
+    <t>チェック3：親値が'N'の場合、サービスコードと費用仕訳レベルは一致しなければならない。0000000000は不可。</t>
+  </si>
+  <si>
+    <t>チェック3：親値が'N'の場合、サービスコードと費用仕訳レベルは一致しなければならない。およびチェック7-03：収益フラグがYでない場合、税金グループはNULLでなければならない。</t>
   </si>
   <si>
     <t>WBSマスタ登録可否フラグをNULLに修正してください。</t>
   </si>
   <si>
-    <t>費用仕訳レベルをサービスコード(2000000001)に修正してください。</t>
+    <t>費用仕訳レベルをサービスコードと同じ値（2000000001）に修正してください。</t>
+  </si>
+  <si>
+    <t>費用仕訳レベルをサービスコードと一致させてください。</t>
+  </si>
+  <si>
+    <t>費用仕訳レベルをサービスコード（2000000003）に修正してください。</t>
+  </si>
+  <si>
+    <t>費用仕訳レベルをサービスコード（2000000004）に修正してください。</t>
+  </si>
+  <si>
+    <t>費用仕訳レベルをサービスコード（2000000005）に修正してください。</t>
+  </si>
+  <si>
+    <t>費用仕訳レベルをサービスコード（2000000006）に修正してください。</t>
+  </si>
+  <si>
+    <t>費用仕訳レベルをサービスコード（2000000007）に修正してください。</t>
+  </si>
+  <si>
+    <t>費用仕訳レベルを修正し、税金グループをNULLにしてください。</t>
   </si>
 </sst>
 </file>
@@ -405,7 +456,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -432,49 +483,210 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" t="s">
-        <v>7</v>
+      <c r="A2">
+        <v>8</v>
       </c>
       <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>19</v>
+      </c>
+      <c r="F2" t="s">
+        <v>23</v>
+      </c>
+      <c r="G2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
         <v>9</v>
       </c>
-      <c r="C2" t="s">
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="C3" t="s">
+        <v>9</v>
+      </c>
+      <c r="D3" t="s">
+        <v>18</v>
+      </c>
+      <c r="E3" t="s">
+        <v>20</v>
+      </c>
+      <c r="F3" t="s">
+        <v>24</v>
+      </c>
+      <c r="G3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="B4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" t="s">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
+      </c>
+      <c r="G4" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>11</v>
+      </c>
+      <c r="B5" t="s">
+        <v>7</v>
+      </c>
+      <c r="C5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s">
+        <v>26</v>
+      </c>
+      <c r="G5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
         <v>12</v>
       </c>
-      <c r="E2" t="s">
+      <c r="B6" t="s">
+        <v>7</v>
+      </c>
+      <c r="C6" t="s">
+        <v>12</v>
+      </c>
+      <c r="D6" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" t="s">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s">
+        <v>24</v>
+      </c>
+      <c r="G6" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>13</v>
+      </c>
+      <c r="B7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" t="s">
+        <v>18</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
+      </c>
+      <c r="F7" t="s">
+        <v>24</v>
+      </c>
+      <c r="G7" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
         <v>14</v>
       </c>
-      <c r="F2" t="s">
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D8" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" t="s">
+        <v>22</v>
+      </c>
+      <c r="F8" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9">
+        <v>15</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
+        <v>15</v>
+      </c>
+      <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>22</v>
+      </c>
+      <c r="F9" t="s">
+        <v>24</v>
+      </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10">
         <v>16</v>
       </c>
-      <c r="G2" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" t="s">
-        <v>15</v>
-      </c>
-      <c r="F3" t="s">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s">
-        <v>19</v>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" t="s">
+        <v>36</v>
       </c>
     </row>
   </sheetData>

--- a/llm_result_ServiceCode4.xlsx
+++ b/llm_result_ServiceCode4.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -462,6 +462,101 @@
       <c r="G1" s="1" t="inlineStr">
         <is>
           <t>修正アドバイス</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B2" t="n">
+        <v>1234</v>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>1000000001</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>WBSマスタ登録可否フラグ</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>チェック2：親値が'Y'の場合、WBSマスタ登録可否フラグはNULLでなければならない。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>WBSマスタ登録可否フラグをNULLに修正してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>7</v>
+      </c>
+      <c r="B3" t="n">
+        <v>1234</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>1000000001</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>事業区分レベル</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>チェック8-01：親値が親（Y）であり、会社コードが再編4社でなく、かつサービスコードが0000000000ではない場合、事業区分レベルは0000000000でなければならない。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>事業区分レベルを'0000000000'に修正してください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>8</v>
+      </c>
+      <c r="B4" t="n">
+        <v>1234</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>2000000001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>費用仕訳レベル</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>9999999999</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>チェック3：親値が'N'の場合、サービスコードと費用仕訳レベルは一致しなければならない。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>費用仕訳レベルをサービスコード（値）'2000000001'に修正してください。</t>
         </is>
       </c>
     </row>
